--- a/output/Jiangsu/盐城市_api_news.xlsx
+++ b/output/Jiangsu/盐城市_api_news.xlsx
@@ -565,14 +565,12 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
       </c>
-      <c r="N2" t="n">
-        <v>8</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/aee344d32e9c4ea5b08b533df8aac83f</t>
@@ -639,14 +637,12 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
       </c>
-      <c r="N3" t="n">
-        <v>12</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/5a6d21bfcbe64863bc377411fe9ab731</t>
@@ -713,14 +709,12 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/acc0b35a8a104b8d83ecc3475ebef46c</t>
@@ -787,14 +781,12 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="M5" t="n">
         <v>6</v>
       </c>
-      <c r="N5" t="n">
-        <v>6</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/77e0899a63274b75a3ab254aeb2aa29b</t>
@@ -861,14 +853,12 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
-      <c r="N6" t="n">
-        <v>15</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/176c9d6d4aad4e15af63c96d0d38e9ca</t>
@@ -935,14 +925,12 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" t="n">
-        <v>6</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/d74a003c18a744cd86a45bcf50701ba6</t>
@@ -1009,14 +997,12 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/d05b2183765644b1a9ce5e67e5068d5a</t>
@@ -1083,14 +1069,12 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M9" t="n">
         <v>2</v>
       </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/8375c11f1e524637b1d058d790a609f6</t>
@@ -1157,14 +1141,12 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" t="n">
-        <v>4</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/02b21f171158441e8056e3a30476b1a6</t>
@@ -1231,14 +1213,12 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/c3d641041dcc45c29fc740c1b2070e5e</t>
@@ -1305,14 +1285,12 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M12" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/0b51ea191c2e4c338e35d1fd0533c96c</t>
@@ -1379,14 +1357,12 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/0ad86a2cb61c4fdbb1834f540e922937</t>
@@ -1453,14 +1429,12 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M14" t="n">
         <v>8</v>
       </c>
-      <c r="N14" t="n">
-        <v>8</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/481fb5973b6546acab120b972309fa51</t>
@@ -1527,14 +1501,12 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M15" t="n">
         <v>8</v>
       </c>
-      <c r="N15" t="n">
-        <v>8</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/18cc47c0a99b4f59a0cd4f957f4fb714</t>
@@ -1601,14 +1573,12 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M16" t="n">
         <v>12</v>
       </c>
-      <c r="N16" t="n">
-        <v>12</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/b816ca3e20ef40d09ff462fa094dae62</t>
@@ -1675,14 +1645,12 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M17" t="n">
         <v>4</v>
       </c>
-      <c r="N17" t="n">
-        <v>4</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/da783858e5de4a809346062d91e8b62d</t>
@@ -1749,14 +1717,12 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" t="n">
-        <v>11</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/1b79227e173049b9a3c35afdd80aaf76</t>
@@ -1823,14 +1789,12 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M19" t="n">
         <v>6</v>
       </c>
-      <c r="N19" t="n">
-        <v>6</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/5fc35c1de1084ee69eec4401aaa53373</t>
@@ -1897,14 +1861,12 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M20" t="n">
         <v>8</v>
       </c>
-      <c r="N20" t="n">
-        <v>8</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/bd8081e9378a4ba48a62a927144b66dc</t>
@@ -1971,14 +1933,12 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M21" t="n">
         <v>8</v>
       </c>
-      <c r="N21" t="n">
-        <v>8</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/e480e4ba8ebc402489f71297104ee6c4</t>
@@ -2045,14 +2005,12 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M22" t="n">
         <v>5</v>
       </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/683359ebed694bb8bb8fae1a47f69f95</t>
@@ -2119,14 +2077,12 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M23" t="n">
         <v>6</v>
       </c>
-      <c r="N23" t="n">
-        <v>6</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/e2b3f5e0e4dd48d0a3118fc7a180a084</t>
@@ -2193,14 +2149,12 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M24" t="n">
         <v>9</v>
       </c>
-      <c r="N24" t="n">
-        <v>9</v>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/f14d41b49e7f4396b895e135b6074bc4</t>
@@ -2267,14 +2221,12 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/19103766826d4bc58a57f03889ffdd4b</t>
@@ -2341,14 +2293,12 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/e49fd32e54ff4b09b1dba5a61826c800</t>
@@ -2415,14 +2365,12 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/d8c47a4ce3564fe1ac912c7eee1c2d7c</t>
@@ -2489,14 +2437,12 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/3eed95bba95e4d789bb803b9ec692bec</t>
@@ -2563,14 +2509,12 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/20be242e17254f52a7256e3855dc8802</t>
@@ -2637,14 +2581,12 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/c01a431c235646a4aacd80e96ce29372</t>
@@ -2711,14 +2653,12 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/dd10ed6a9b964b5fbbe208a0fa12420c</t>
@@ -2785,14 +2725,12 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/cce4d3eb014a49848cfe26e702a1bdd7</t>
@@ -2859,14 +2797,12 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/ddde0af284064de986c3958bc804f3cc</t>
@@ -2933,14 +2869,12 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/3d96691d26b047bbbd9c882264e8b141</t>
@@ -3007,14 +2941,12 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/2e7fa7145bb04c978d6e5edbab3c881f</t>
@@ -3081,14 +3013,12 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/338567240cc94be99d4d05d4cc55cfea</t>
@@ -3155,14 +3085,12 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/d392586ac001485cbb07f41ace900829</t>
@@ -3229,14 +3157,12 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M38" t="n">
         <v>18</v>
       </c>
-      <c r="N38" t="n">
-        <v>18</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/3ec8937ffaf04f59b0270794cd70b336</t>
@@ -3303,14 +3229,12 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M39" t="n">
         <v>6</v>
       </c>
-      <c r="N39" t="n">
-        <v>6</v>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/6cd6a73f1ebd4c78b9f4b3ac38b4dd64</t>
@@ -3377,14 +3301,12 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M40" t="n">
         <v>10</v>
       </c>
-      <c r="N40" t="n">
-        <v>10</v>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/a6fbe936a43246d0b56af361a1726dd7</t>
@@ -3451,14 +3373,12 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M41" t="n">
         <v>8</v>
       </c>
-      <c r="N41" t="n">
-        <v>8</v>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/c83585c61d0f4852adc0867878a1b305</t>
@@ -3525,14 +3445,12 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M42" t="n">
         <v>3</v>
       </c>
-      <c r="N42" t="n">
-        <v>3</v>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/5dd9d5dd35d34bc7a3bf00702bf73a90</t>
@@ -3599,14 +3517,12 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M43" t="n">
         <v>8</v>
       </c>
-      <c r="N43" t="n">
-        <v>8</v>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/96bdc8692eab48f398506d0c4e9e8b8e</t>
@@ -3673,14 +3589,12 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M44" t="n">
         <v>8</v>
       </c>
-      <c r="N44" t="n">
-        <v>8</v>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/f2efcabbc39948b5a9274d14dad2d7f3</t>
@@ -3747,14 +3661,12 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M45" t="n">
         <v>8</v>
       </c>
-      <c r="N45" t="n">
-        <v>8</v>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/2c001c3987634790a0541f01143deab9</t>
@@ -3821,14 +3733,12 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="M46" t="n">
         <v>10</v>
       </c>
-      <c r="N46" t="n">
-        <v>10</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/09b61a7a67f64227a61206485704ee46</t>
@@ -3895,14 +3805,12 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M47" t="n">
         <v>6</v>
       </c>
-      <c r="N47" t="n">
-        <v>6</v>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/1740932b5e884516827af779757eaba5</t>
@@ -3969,14 +3877,12 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M48" t="n">
         <v>11</v>
       </c>
-      <c r="N48" t="n">
-        <v>11</v>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/191c480d70a64da7a688f402bddafa58</t>
@@ -4043,14 +3949,12 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M49" t="n">
         <v>7</v>
       </c>
-      <c r="N49" t="n">
-        <v>7</v>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/30ae18657e0940128c9cb641359b6d58</t>
@@ -4117,14 +4021,12 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M50" t="n">
         <v>8</v>
       </c>
-      <c r="N50" t="n">
-        <v>8</v>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/3783ad3de21d47429c3a8cf89876d6d4</t>
@@ -4191,14 +4093,12 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M51" t="n">
         <v>7</v>
       </c>
-      <c r="N51" t="n">
-        <v>7</v>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/4b8345eb281d4f3b84e9e17f196f4ff4</t>
@@ -4265,14 +4165,12 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M52" t="n">
         <v>8</v>
       </c>
-      <c r="N52" t="n">
-        <v>8</v>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/64131384fab0464e925a4b6c15a8af76</t>
@@ -4339,14 +4237,12 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M53" t="n">
         <v>20</v>
       </c>
-      <c r="N53" t="n">
-        <v>20</v>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/a2ec8564f0ea4ad295a08d2f5a2ec997</t>
@@ -4413,14 +4309,12 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M54" t="n">
         <v>9</v>
       </c>
-      <c r="N54" t="n">
-        <v>9</v>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/bb64e2074ee848abb184642a876b67d3</t>
@@ -4487,14 +4381,12 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M55" t="n">
         <v>6</v>
       </c>
-      <c r="N55" t="n">
-        <v>6</v>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/e7be46f22891433598b89639f91f7548</t>
@@ -4561,14 +4453,12 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M56" t="n">
         <v>4</v>
       </c>
-      <c r="N56" t="n">
-        <v>4</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/9646646e893e4f489f26061ea24bbaf8</t>
@@ -4635,14 +4525,12 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M57" t="n">
         <v>4</v>
       </c>
-      <c r="N57" t="n">
-        <v>4</v>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/974105eaddb74a629217903ef5e8a7c7</t>
@@ -4709,14 +4597,12 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M58" t="n">
         <v>4</v>
       </c>
-      <c r="N58" t="n">
-        <v>4</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/466fc34c5fbc4aa3adb98305f200d395</t>
@@ -4783,14 +4669,12 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M59" t="n">
         <v>8</v>
       </c>
-      <c r="N59" t="n">
-        <v>8</v>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/32a9e29d8cd848829fe775449b6d2ffc</t>
@@ -4857,14 +4741,12 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M60" t="n">
         <v>2</v>
       </c>
-      <c r="N60" t="n">
-        <v>2</v>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/ddc8303303334bb3b617f606a0ae63fa</t>
@@ -4931,14 +4813,12 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M61" t="n">
         <v>2</v>
       </c>
-      <c r="N61" t="n">
-        <v>2</v>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/5a805b206df647bfb7989e479358c982</t>
@@ -5005,14 +4885,12 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M62" t="n">
         <v>8</v>
       </c>
-      <c r="N62" t="n">
-        <v>8</v>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/0b515f6082b9498e89bbb3b4b9037ad9</t>
@@ -5079,14 +4957,12 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M63" t="n">
         <v>8</v>
       </c>
-      <c r="N63" t="n">
-        <v>8</v>
-      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/550e889dc1014bc8b710d55b16914532</t>
@@ -5153,14 +5029,12 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M64" t="n">
         <v>6</v>
       </c>
-      <c r="N64" t="n">
-        <v>6</v>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/f6a3ceacccab4c228b1b65900ba7f335</t>
@@ -5227,14 +5101,12 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M65" t="n">
         <v>4</v>
       </c>
-      <c r="N65" t="n">
-        <v>4</v>
-      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/ed85cd103a6c46bb8343bcfa4f1c6a96</t>
@@ -5301,14 +5173,12 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/1930fd27775e4c1a99b1936d0b95e7e2</t>
@@ -5375,14 +5245,12 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/f45851edb1814e62a08e61449bc6c82c</t>
@@ -5449,14 +5317,12 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/574f6d66f47b4bba9c769c11d27e5098</t>
@@ -5523,14 +5389,12 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/f9fff8810b0e4da89873017e08b0aa71</t>
@@ -5597,14 +5461,12 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
       </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/f2f945127ff54912997e4ec073a41e8f</t>
@@ -5671,14 +5533,12 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/681a33d47871406caa3a241fff141559</t>
@@ -5745,14 +5605,12 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/3a474744f3614ff6bd9d289a8777aa86</t>
@@ -5819,14 +5677,12 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M73" t="n">
         <v>13</v>
       </c>
-      <c r="N73" t="n">
-        <v>13</v>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/26b0a3c63ec246cc9573b30cccd6cd14</t>
@@ -5893,14 +5749,12 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M74" t="n">
         <v>8</v>
       </c>
-      <c r="N74" t="n">
-        <v>8</v>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/03c1ea5fdd3c4756a74b76822254790f</t>
@@ -5967,14 +5821,12 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M75" t="n">
         <v>2</v>
       </c>
-      <c r="N75" t="n">
-        <v>2</v>
-      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/0e1a97abb5ad411789314b57f035043d</t>
@@ -6041,14 +5893,12 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M76" t="n">
         <v>10</v>
       </c>
-      <c r="N76" t="n">
-        <v>10</v>
-      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/2080883a8b5544a3a3889d46d1b2287f</t>
@@ -6115,14 +5965,12 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M77" t="n">
         <v>8</v>
       </c>
-      <c r="N77" t="n">
-        <v>8</v>
-      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/3b4a155ad3d14eb296eac6b4681d2d81</t>
@@ -6189,14 +6037,12 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M78" t="n">
         <v>6</v>
       </c>
-      <c r="N78" t="n">
-        <v>6</v>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/664f8059696d49518aaa46cd3d18426c</t>
@@ -6263,14 +6109,12 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M79" t="n">
         <v>6</v>
       </c>
-      <c r="N79" t="n">
-        <v>6</v>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/9cd1c331a1d84aea845acaa35fdc4fb2</t>
@@ -6337,14 +6181,12 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M80" t="n">
         <v>3</v>
       </c>
-      <c r="N80" t="n">
-        <v>3</v>
-      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/cca04ba9950a4784b7fc5041bddf054f</t>
@@ -6411,14 +6253,12 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M81" t="n">
         <v>2</v>
       </c>
-      <c r="N81" t="n">
-        <v>2</v>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/e958885fb6584ebb800ccd05edc0c34c</t>
@@ -6485,14 +6325,12 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M82" t="n">
         <v>2</v>
       </c>
-      <c r="N82" t="n">
-        <v>2</v>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/eb48c4aa70a14eca883794892be884a0</t>
@@ -6559,14 +6397,12 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M83" t="n">
         <v>2</v>
       </c>
-      <c r="N83" t="n">
-        <v>2</v>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/fd0eaaf961e74d8ea57efee7da08e0e6</t>
@@ -6633,14 +6469,12 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M84" t="n">
         <v>8</v>
       </c>
-      <c r="N84" t="n">
-        <v>8</v>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/201ca49e79604e7b90955b964ce63a46</t>
@@ -6707,14 +6541,12 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M85" t="n">
         <v>8</v>
       </c>
-      <c r="N85" t="n">
-        <v>8</v>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/06de4da95c1944fe94d4de85930a001d</t>
@@ -6781,14 +6613,12 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M86" t="n">
         <v>9</v>
       </c>
-      <c r="N86" t="n">
-        <v>9</v>
-      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/1c36a92343ec42d596c5fe4d1daa1f6b</t>
@@ -6855,14 +6685,12 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M87" t="n">
         <v>11</v>
       </c>
-      <c r="N87" t="n">
-        <v>11</v>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/22adc6a0ffb94660818262c98b333e0c</t>
@@ -6929,14 +6757,12 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M88" t="n">
         <v>9</v>
       </c>
-      <c r="N88" t="n">
-        <v>9</v>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/4b890db4d00b4ecebba7253421572b34</t>
@@ -7003,14 +6829,12 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M89" t="n">
         <v>9</v>
       </c>
-      <c r="N89" t="n">
-        <v>9</v>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/8bd8dec8ea3b4d089b13d8cbf49a2207</t>
@@ -7077,14 +6901,12 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M90" t="n">
         <v>8</v>
       </c>
-      <c r="N90" t="n">
-        <v>8</v>
-      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/80cec24118a445b1a621429db1c4cdba</t>
@@ -7151,14 +6973,12 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M91" t="n">
         <v>8</v>
       </c>
-      <c r="N91" t="n">
-        <v>8</v>
-      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/ae99b5c093b945f88abdcac93ca03958</t>
@@ -7225,14 +7045,12 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M92" t="n">
         <v>8</v>
       </c>
-      <c r="N92" t="n">
-        <v>8</v>
-      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/b876f22bcc9c4730883faa19fe5d83b5</t>
@@ -7299,14 +7117,12 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M93" t="n">
         <v>18</v>
       </c>
-      <c r="N93" t="n">
-        <v>18</v>
-      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/84ab19cbde9643afa0ad4261fc799889</t>
@@ -7373,14 +7189,12 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/732db63d9cb4473793794f7b292cb80b</t>
@@ -7447,14 +7261,12 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M95" t="n">
         <v>8</v>
       </c>
-      <c r="N95" t="n">
-        <v>8</v>
-      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/1843918fe827463bbed0a34fefdc3787</t>
@@ -7521,14 +7333,12 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M96" t="n">
         <v>8</v>
       </c>
-      <c r="N96" t="n">
-        <v>8</v>
-      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/0294039886354b2da18fce0c9edcfaa3</t>
@@ -7595,14 +7405,12 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M97" t="n">
         <v>8</v>
       </c>
-      <c r="N97" t="n">
-        <v>8</v>
-      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/1e96b03cc08c48f7a092203ce571b53c</t>
@@ -7669,14 +7477,12 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M98" t="n">
         <v>10</v>
       </c>
-      <c r="N98" t="n">
-        <v>10</v>
-      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/ae2145eb7cbd43c29c4a31c46f8f0af2</t>
@@ -7743,14 +7549,12 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M99" t="n">
         <v>8</v>
       </c>
-      <c r="N99" t="n">
-        <v>8</v>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/064e8592bf50492da7a70bfd7e8797db</t>
@@ -7817,14 +7621,12 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M100" t="n">
         <v>6</v>
       </c>
-      <c r="N100" t="n">
-        <v>6</v>
-      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/10c7d767bf2047c19479c045258d531c</t>
@@ -7891,14 +7693,12 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M101" t="n">
         <v>8</v>
       </c>
-      <c r="N101" t="n">
-        <v>8</v>
-      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/09cf1d4e06484154ae9ef9ef9d76f9c5</t>
@@ -7965,14 +7765,12 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M102" t="n">
         <v>10</v>
       </c>
-      <c r="N102" t="n">
-        <v>10</v>
-      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/00cefad332a840cbba6342c6238169bc</t>
@@ -8039,14 +7837,12 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M103" t="n">
         <v>9</v>
       </c>
-      <c r="N103" t="n">
-        <v>9</v>
-      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/4016312c3a1849248d82c580506ca1e4</t>
@@ -8113,14 +7909,12 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M104" t="n">
         <v>9</v>
       </c>
-      <c r="N104" t="n">
-        <v>9</v>
-      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/10d19681fa1144829484309ff50b46c1</t>
@@ -8187,14 +7981,12 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M105" t="n">
         <v>2</v>
       </c>
-      <c r="N105" t="n">
-        <v>2</v>
-      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/fea7ca85b30c4615ba04bce54a41d99f</t>
@@ -8261,14 +8053,12 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M106" t="n">
         <v>3</v>
       </c>
-      <c r="N106" t="n">
-        <v>3</v>
-      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/4fc4db1f1c5747109985d5dbf296b00a</t>
@@ -8335,14 +8125,12 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M107" t="n">
         <v>2</v>
       </c>
-      <c r="N107" t="n">
-        <v>2</v>
-      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/099d0edce24749568340cd3d9d3c14bc</t>
@@ -8409,14 +8197,12 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M108" t="n">
         <v>2</v>
       </c>
-      <c r="N108" t="n">
-        <v>2</v>
-      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/5a71a4dc37204f2c9e0cc37e8c613024</t>
@@ -8483,14 +8269,12 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M109" t="n">
         <v>2</v>
       </c>
-      <c r="N109" t="n">
-        <v>2</v>
-      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/7b8bd71193124f239aba32d346985ce1</t>
@@ -8557,14 +8341,12 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M110" t="n">
         <v>2</v>
       </c>
-      <c r="N110" t="n">
-        <v>2</v>
-      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/3a401cdbca0147f3a05b07a7da12dc4a</t>
@@ -8631,14 +8413,12 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M111" t="n">
         <v>6</v>
       </c>
-      <c r="N111" t="n">
-        <v>6</v>
-      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/3c689f6f0bea43e2a42183a96d156e66</t>
@@ -8705,14 +8485,12 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
       </c>
-      <c r="N112" t="n">
-        <v>0</v>
-      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/20ef9d82afc04d8a83ac83e87cb8be66</t>
@@ -8779,14 +8557,12 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
       </c>
-      <c r="N113" t="n">
-        <v>0</v>
-      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/158b08c5056648408573f6839f93a45a</t>
@@ -8853,14 +8629,12 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
       </c>
-      <c r="N114" t="n">
-        <v>0</v>
-      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/3776a4e1ac4a491caa5fc52fc7f7b2a5</t>
@@ -8927,14 +8701,12 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
       </c>
-      <c r="N115" t="n">
-        <v>0</v>
-      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/4260181c9d7843be8d46c8b34e746dfe</t>
@@ -9001,14 +8773,12 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
       </c>
-      <c r="N116" t="n">
-        <v>0</v>
-      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/5c4f3fafa55c4818bbfa143643553fe8</t>
@@ -9075,14 +8845,12 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
       </c>
-      <c r="N117" t="n">
-        <v>0</v>
-      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/663e203c486741d8b37ec131e8f18cd1</t>
@@ -9149,14 +8917,12 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
       </c>
-      <c r="N118" t="n">
-        <v>0</v>
-      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/870542cf9c334879a9504ef1e1645060</t>
@@ -9223,14 +8989,12 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
       </c>
-      <c r="N119" t="n">
-        <v>0</v>
-      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/89d236ff7480418a82fe074ee25666ca</t>
@@ -9297,14 +9061,12 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
       </c>
-      <c r="N120" t="n">
-        <v>0</v>
-      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/cdc9543c46fb484fab73515335f1be62</t>
@@ -9371,14 +9133,12 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
       </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/df76dc9134d04185b519b00b6b87ed08</t>
@@ -9445,14 +9205,12 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M122" t="n">
         <v>8</v>
       </c>
-      <c r="N122" t="n">
-        <v>8</v>
-      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/59700eb2ed494e13a820415df2781dd5</t>
@@ -9519,14 +9277,12 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
       </c>
-      <c r="N123" t="n">
-        <v>0</v>
-      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/54649bdcdd3b48678031bd7bb314bae3</t>
@@ -9593,14 +9349,12 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
       </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/923d8a1d732d457583ff5e01af2bc6ea</t>
@@ -9667,14 +9421,12 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
       </c>
-      <c r="N125" t="n">
-        <v>0</v>
-      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/234eb560e949430ebb1d310ee8154eda</t>
@@ -9741,14 +9493,12 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
       </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/c9fc7a78bbbf462fbf6795f8899e07c2</t>
@@ -9815,14 +9565,12 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
       </c>
-      <c r="N127" t="n">
-        <v>0</v>
-      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/099db4752d314848a85e97a8671ada43</t>
@@ -9889,14 +9637,12 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
       </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/da80266ee113433e867d2ba71ae20ef5</t>
@@ -9963,14 +9709,12 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
       </c>
-      <c r="N129" t="n">
-        <v>0</v>
-      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/8da7e6c1dc6349ee9353176daa904e32</t>
@@ -10037,14 +9781,12 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
       </c>
-      <c r="N130" t="n">
-        <v>0</v>
-      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/4d18449bf66447a8866cb9b7823acce6</t>
@@ -10111,14 +9853,12 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M131" t="n">
         <v>21</v>
       </c>
-      <c r="N131" t="n">
-        <v>21</v>
-      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/00aeca3f7d6c44fe957a24caa179a536</t>
@@ -10185,14 +9925,12 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M132" t="n">
         <v>14</v>
       </c>
-      <c r="N132" t="n">
-        <v>14</v>
-      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/01c359d90367476a9bf67170bf415134</t>
@@ -10259,14 +9997,12 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M133" t="n">
         <v>8</v>
       </c>
-      <c r="N133" t="n">
-        <v>8</v>
-      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/da1c90e367ac48868f9a0b0571d03048</t>
@@ -10333,14 +10069,12 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M134" t="n">
         <v>11</v>
       </c>
-      <c r="N134" t="n">
-        <v>11</v>
-      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/862f9b6c313a485bbeda9159737ce82c</t>
@@ -10407,14 +10141,12 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M135" t="n">
         <v>6</v>
       </c>
-      <c r="N135" t="n">
-        <v>6</v>
-      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/5e0e01a8afcf468ba651ac3fc4807161</t>
@@ -10481,14 +10213,12 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M136" t="n">
         <v>10</v>
       </c>
-      <c r="N136" t="n">
-        <v>10</v>
-      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/910bb0d815694f209cc77f60715c863b</t>
@@ -10555,14 +10285,12 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M137" t="n">
         <v>6</v>
       </c>
-      <c r="N137" t="n">
-        <v>6</v>
-      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/6ff08d6ae58a4ca980e377fad14952bb</t>
@@ -10629,14 +10357,12 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="M138" t="n">
         <v>8</v>
       </c>
-      <c r="N138" t="n">
-        <v>8</v>
-      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/237ee986709a48698d30b69c794bff94</t>
@@ -10703,14 +10429,12 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M139" t="n">
         <v>2</v>
       </c>
-      <c r="N139" t="n">
-        <v>2</v>
-      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
           <t>https://www.yancheng.gov.cn/opendata/interface/detail/627301c56b7a48de922e5b04dbd6eb84</t>
